--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_29-12-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_29-12-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="159">
   <si>
     <t>SKU</t>
   </si>
@@ -253,7 +253,7 @@
     <t>£31.66</t>
   </si>
   <si>
-    <t>£63.71</t>
+    <t>Error: 'NoneType' object has no attribute 'find_all'</t>
   </si>
   <si>
     <t>£62.80</t>
@@ -403,22 +403,58 @@
     <t>£67.76</t>
   </si>
   <si>
+    <t>£24.78</t>
+  </si>
+  <si>
+    <t>£28.72</t>
+  </si>
+  <si>
+    <t>£31.91</t>
+  </si>
+  <si>
+    <t>£37.78</t>
+  </si>
+  <si>
+    <t>£43.78</t>
+  </si>
+  <si>
+    <t>£48.11</t>
+  </si>
+  <si>
+    <t>£52.17</t>
+  </si>
+  <si>
+    <t>£45.88</t>
+  </si>
+  <si>
+    <t>£53.74</t>
+  </si>
+  <si>
+    <t>£54.67</t>
+  </si>
+  <si>
+    <t>£64.44</t>
+  </si>
+  <si>
+    <t>£76.10</t>
+  </si>
+  <si>
+    <t>£25.45</t>
+  </si>
+  <si>
+    <t>£25.10</t>
+  </si>
+  <si>
+    <t>£32.15</t>
+  </si>
+  <si>
+    <t>£37.40</t>
+  </si>
+  <si>
+    <t>£38.50</t>
+  </si>
+  <si>
     <t>POA</t>
-  </si>
-  <si>
-    <t>£25.45</t>
-  </si>
-  <si>
-    <t>£25.10</t>
-  </si>
-  <si>
-    <t>£32.15</t>
-  </si>
-  <si>
-    <t>£37.40</t>
-  </si>
-  <si>
-    <t>£38.50</t>
   </si>
   <si>
     <t>£11.40</t>
@@ -897,7 +933,7 @@
         <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N2" t="s">
         <v>44</v>
@@ -935,16 +971,16 @@
         <v>115</v>
       </c>
       <c r="K3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L3" t="s">
         <v>60</v>
       </c>
       <c r="M3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N3" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -979,16 +1015,16 @@
         <v>116</v>
       </c>
       <c r="K4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L4" t="s">
         <v>61</v>
       </c>
       <c r="M4" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N4" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1023,16 +1059,16 @@
         <v>117</v>
       </c>
       <c r="K5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="L5" t="s">
         <v>47</v>
       </c>
       <c r="M5" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N5" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1067,16 +1103,16 @@
         <v>118</v>
       </c>
       <c r="K6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L6" t="s">
         <v>48</v>
       </c>
       <c r="M6" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N6" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1111,16 +1147,16 @@
         <v>119</v>
       </c>
       <c r="K7" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="L7" t="s">
         <v>63</v>
       </c>
       <c r="M7" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N7" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1155,16 +1191,16 @@
         <v>120</v>
       </c>
       <c r="K8" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L8" t="s">
         <v>63</v>
       </c>
       <c r="M8" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N8" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1199,16 +1235,16 @@
         <v>121</v>
       </c>
       <c r="K9" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s">
         <v>64</v>
       </c>
       <c r="M9" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N9" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1243,16 +1279,16 @@
         <v>122</v>
       </c>
       <c r="K10" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1287,13 +1323,13 @@
         <v>123</v>
       </c>
       <c r="K11" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="M11" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s">
         <v>53</v>
@@ -1334,13 +1370,13 @@
         <v>54</v>
       </c>
       <c r="L12" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="M12" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N12" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1375,16 +1411,16 @@
         <v>125</v>
       </c>
       <c r="K13" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L13" t="s">
         <v>55</v>
       </c>
       <c r="M13" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N13" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1422,13 +1458,13 @@
         <v>54</v>
       </c>
       <c r="L14" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="M14" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N14" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1466,13 +1502,13 @@
         <v>54</v>
       </c>
       <c r="L15" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="M15" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1507,16 +1543,16 @@
         <v>128</v>
       </c>
       <c r="K16" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="L16" t="s">
         <v>58</v>
       </c>
       <c r="M16" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="N16" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_29-12-2025.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_29-12-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="147">
   <si>
     <t>SKU</t>
   </si>
@@ -244,7 +244,7 @@
     <t>£41.33</t>
   </si>
   <si>
-    <t>£45.39</t>
+    <t>Error: 'NoneType' object has no attribute 'find_all'</t>
   </si>
   <si>
     <t>£49.14</t>
@@ -253,7 +253,7 @@
     <t>£31.66</t>
   </si>
   <si>
-    <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+    <t>£63.71</t>
   </si>
   <si>
     <t>£62.80</t>
@@ -403,40 +403,7 @@
     <t>£67.76</t>
   </si>
   <si>
-    <t>£24.78</t>
-  </si>
-  <si>
-    <t>£28.72</t>
-  </si>
-  <si>
-    <t>£31.91</t>
-  </si>
-  <si>
-    <t>£37.78</t>
-  </si>
-  <si>
-    <t>£43.78</t>
-  </si>
-  <si>
-    <t>£48.11</t>
-  </si>
-  <si>
-    <t>£52.17</t>
-  </si>
-  <si>
-    <t>£45.88</t>
-  </si>
-  <si>
-    <t>£53.74</t>
-  </si>
-  <si>
-    <t>£54.67</t>
-  </si>
-  <si>
-    <t>£64.44</t>
-  </si>
-  <si>
-    <t>£76.10</t>
+    <t>POA</t>
   </si>
   <si>
     <t>£25.45</t>
@@ -454,9 +421,6 @@
     <t>£38.50</t>
   </si>
   <si>
-    <t>POA</t>
-  </si>
-  <si>
     <t>£11.40</t>
   </si>
   <si>
@@ -490,7 +454,7 @@
     <t>£37.59</t>
   </si>
   <si>
-    <t>£37.43</t>
+    <t>POA or OOS</t>
   </si>
 </sst>
 </file>
@@ -933,7 +897,7 @@
         <v>44</v>
       </c>
       <c r="M2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N2" t="s">
         <v>44</v>
@@ -971,16 +935,16 @@
         <v>115</v>
       </c>
       <c r="K3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L3" t="s">
         <v>60</v>
       </c>
       <c r="M3" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1015,16 +979,16 @@
         <v>116</v>
       </c>
       <c r="K4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L4" t="s">
         <v>61</v>
       </c>
       <c r="M4" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N4" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1059,16 +1023,16 @@
         <v>117</v>
       </c>
       <c r="K5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="L5" t="s">
         <v>47</v>
       </c>
       <c r="M5" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N5" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1103,16 +1067,16 @@
         <v>118</v>
       </c>
       <c r="K6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L6" t="s">
         <v>48</v>
       </c>
       <c r="M6" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1147,16 +1111,16 @@
         <v>119</v>
       </c>
       <c r="K7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="L7" t="s">
         <v>63</v>
       </c>
       <c r="M7" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N7" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1191,16 +1155,16 @@
         <v>120</v>
       </c>
       <c r="K8" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s">
         <v>63</v>
       </c>
       <c r="M8" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1235,16 +1199,16 @@
         <v>121</v>
       </c>
       <c r="K9" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="L9" t="s">
         <v>64</v>
       </c>
       <c r="M9" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N9" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1279,16 +1243,16 @@
         <v>122</v>
       </c>
       <c r="K10" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="L10" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="M10" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N10" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1323,13 +1287,13 @@
         <v>123</v>
       </c>
       <c r="K11" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="L11" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="M11" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N11" t="s">
         <v>53</v>
@@ -1370,13 +1334,13 @@
         <v>54</v>
       </c>
       <c r="L12" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="M12" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N12" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1411,16 +1375,16 @@
         <v>125</v>
       </c>
       <c r="K13" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s">
         <v>55</v>
       </c>
       <c r="M13" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="N13" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1458,13 +1422,13 @@
         <v>54</v>
       </c>
       <c r="L14" t="s">
+        <v>133</v>
+      </c>
+      <c r="M14" t="s">
+        <v>129</v>
+      </c>
+      <c r="N14" t="s">
         <v>144</v>
-      </c>
-      <c r="M14" t="s">
-        <v>146</v>
-      </c>
-      <c r="N14" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1502,13 +1466,13 @@
         <v>54</v>
       </c>
       <c r="L15" t="s">
+        <v>134</v>
+      </c>
+      <c r="M15" t="s">
+        <v>129</v>
+      </c>
+      <c r="N15" t="s">
         <v>145</v>
-      </c>
-      <c r="M15" t="s">
-        <v>146</v>
-      </c>
-      <c r="N15" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1543,16 +1507,16 @@
         <v>128</v>
       </c>
       <c r="K16" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s">
         <v>58</v>
       </c>
       <c r="M16" t="s">
+        <v>129</v>
+      </c>
+      <c r="N16" t="s">
         <v>146</v>
-      </c>
-      <c r="N16" t="s">
-        <v>158</v>
       </c>
     </row>
   </sheetData>
